--- a/data/sites/sales/Sales Playbooks/global-deal-desk-and-territory-quota-workbook (edited copy).xlsx
+++ b/data/sites/sales/Sales Playbooks/global-deal-desk-and-territory-quota-workbook (edited copy).xlsx
@@ -16,9 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Sign-off" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,36 +278,6 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -832,7 +800,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Global Deal Desk and Territory Quota Workbook - Section 10: Cross-Functional Dependencies</t>
+          <t>Global Deal Desk and Territory Quota Workbook - Section 10: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -846,7 +814,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive commercial operations workbook tracking regional quota attainment, discount exception logs, pipeline stage velocity, and multi-year contract terms. Section 10 (Cross-Functional Dependencies) applies to Sales Playbooks within Sales &amp; Marketing Knowledge Hub and is maintained by Marcus Lee. Documents upstream and downstream team dependencies and service-level commitments.</t>
+          <t>Comprehensive commercial operations workbook tracking regional quota attainment, discount exception logs, pipeline stage velocity, and multi-year contract terms. Section 10 (Appendix, Lineage &amp; Sign-off) applies to Sales Playbooks within Sales &amp; Marketing Knowledge Hub and is maintained by Marcus Lee. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
@@ -1014,435 +982,6 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>• Section 10 review cadence is tracked by Marcus Lee under Sales Playbooks governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Global Deal Desk and Territory Quota Workbook - Section 11: Continuous Improvement Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Sales Playbooks | Owner: Marcus Lee  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Comprehensive commercial operations workbook tracking regional quota attainment, discount exception logs, pipeline stage velocity, and multi-year contract terms. Section 11 (Continuous Improvement Roadmap) applies to Sales Playbooks within Sales &amp; Marketing Knowledge Hub and is maintained by Marcus Lee. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 11.1: Tracks proposal turnaround times against the 2-business-day Deal Desk SLA. Secondary control 11.2: Reconciles bookings, expansion ARR, and net dollar retention by segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Pipeline Coverage</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Quota Attainment</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Avg Discount</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.8x</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>11.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>104%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.4x</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>108%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>10.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.9x</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-11</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3.4x</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>108%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stage 11 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Tracks proposal turnaround times against the 2-business-day Deal Desk SLA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Reconciles bookings, expansion ARR, and net dollar retention by segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 11 review cadence is tracked by Marcus Lee under Sales Playbooks governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Global Deal Desk and Territory Quota Workbook - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Sales Playbooks | Owner: Marcus Lee  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Comprehensive commercial operations workbook tracking regional quota attainment, discount exception logs, pipeline stage velocity, and multi-year contract terms. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Sales Playbooks within Sales &amp; Marketing Knowledge Hub and is maintained by Marcus Lee. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: Reconciles bookings, expansion ARR, and net dollar retention by segment. Secondary control 12.2: Monitors pipeline coverage ratios across West, Central, East, and EMEA territories.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Pipeline Coverage</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Quota Attainment</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Avg Discount</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.8x</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>11.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>104%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.4x</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>108%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>10.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.9x</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.9x</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Reconciles bookings, expansion ARR, and net dollar retention by segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Monitors pipeline coverage ratios across West, Central, East, and EMEA territories.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Marcus Lee under Sales Playbooks governance.</t>
         </is>
       </c>
     </row>
